--- a/docs/산출물/06_한결공조_AS관리_인터페이스_정의서_V1.1.xlsx
+++ b/docs/산출물/06_한결공조_AS관리_인터페이스_정의서_V1.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\my-first-project\docs\산출물\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92545627-5140-4890-A88D-5367D0920E3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BCB2BC-B13C-478C-ABFF-016DCA789CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="1" r:id="rId1"/>
@@ -43,10 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="471">
-  <si>
-    <t>[ SFDC 해외 확장 프로젝트 ]</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="474">
   <si>
     <t>인터페이스 리스트 및 정의서</t>
   </si>
@@ -130,15 +127,6 @@
   </si>
   <si>
     <t>시트(상세)</t>
-  </si>
-  <si>
-    <t>Z_SD_PART_ODGI_EUDP</t>
-  </si>
-  <si>
-    <t>IF_HANGYEOL_EU_SFDC_0001</t>
-  </si>
-  <si>
-    <t>트랙터 부품 출고정보 EUDP로 I/F</t>
   </si>
   <si>
     <t>SFDC</t>
@@ -338,9 +326,6 @@
     <t>[ 한결공조 AS 관리 시스템 ]</t>
   </si>
   <si>
-    <t>06.(한결공조 AS 관리 시스템) 인터페이스 정의서_V1.0</t>
-  </si>
-  <si>
     <t>한결공조 AS 관리 시스템</t>
   </si>
   <si>
@@ -546,12 +531,6 @@
   </si>
   <si>
     <t>ERP 재고 변동 → Salesforce 재고 (푸시)</t>
-  </si>
-  <si>
-    <t>IF_ERP_VANSTOCK_0001 재고 변동 푸시</t>
-  </si>
-  <si>
-    <t>ERP에서만 생긴 입고·조정을 ERP가 저장 직후 Salesforce Apex REST로 보내 재고(ProductItem)에 변동량만큼 반영</t>
   </si>
   <si>
     <t>주 경로. 실패해도 IF-02-R(매시 30분)이 같은 변동을 가져옴. 이력 번호로 한 번만 반영</t>
@@ -825,12 +804,6 @@
     <t>ERP 재고 변동 → Salesforce 재고 (가져오기, 안전망)</t>
   </si>
   <si>
-    <t>IF_ERP_VANSTOCK_0001 재고 변동 가져오기</t>
-  </si>
-  <si>
-    <t>Salesforce가 매시 30분 ERP 이력에서 "마지막으로 가져온 번호 이후"만 조회해 푸시로 못 받은 변동을 반영</t>
-  </si>
-  <si>
     <t>예약 "HG ERP 재고 동기화 :30 (매시, 푸시 안전망)" → ErpStockSyncBatch(scope 1 = 한 쪽 200건, 최대 10쪽) → ErpStockSyncService.syncNextPage</t>
   </si>
   <si>
@@ -957,12 +930,6 @@
     <t>사용 부품 → ERP 재고 차감</t>
   </si>
   <si>
-    <t>IF_ERP_CONSUME_0001 사용 부품 차감</t>
-  </si>
-  <si>
-    <t>기사가 출동에서 사용 부품을 저장하면 ERP의 같은 위치(창고·기사 차량) 재고를 차감</t>
-  </si>
-  <si>
     <t>ProductConsumedTrigger → ErpSyncQueueable → ErpInventoryService. 200건 = 콜아웃 1번</t>
   </si>
   <si>
@@ -1123,12 +1090,6 @@
   </si>
   <si>
     <t>재고 이동(창고 → 기사 차량) → ERP</t>
-  </si>
-  <si>
-    <t>IF_ERP_TRANSFER_0001 재고 이동</t>
-  </si>
-  <si>
-    <t>창고에서 기사 차량으로 보충한 재고 이동(ProductTransfer)을 기사가 수령하면 ERP에서도 출발 위치 차감·도착 위치 증가</t>
   </si>
   <si>
     <t>ProductTransferTrigger → ErpSyncQueueable → ErpInventoryService. 200건 = 콜아웃 1번</t>
@@ -1233,12 +1194,6 @@
   </si>
   <si>
     <t>도로명주소 검색 (사업장·고객사 주소)</t>
-  </si>
-  <si>
-    <t>IF_JUSO_ADDRESS_0001 도로명주소 검색</t>
-  </si>
-  <si>
-    <t>상담원·센터장이 사업장·고객사 주소를 도로명주소 API로 검색해 입력, 사업장은 행정구역 코드로 서비스센터 자동 지정</t>
   </si>
   <si>
     <t>AddressSearchController.searchAddresses / saveSiteAddress → CustomerSiteAddressService · ServiceCenterMappingService</t>
@@ -1467,9 +1422,6 @@
   <si>
     <t>2026. 10. 16.</t>
     <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>IF-01 비고: 단가 원천은 ERP, 이번 범위는 초기 이관값을 Salesforce 제품 ERP 단가(+ 가격표 항목)에 둠, ERP Mock에는 단가 없음, 부품 마스터 동기화는 다음 단계 / IF-03: 사용 부품 삭제 시 재고 되돌림은 Salesforce 표준(Apex 되돌림 제거, R6). 나머지 IF는 변경 없음</t>
   </si>
   <si>
     <t>ERP 부품 코드·이름·분류·단가 → Product2. 범위 밖: 초기 이관(Data Loader, 외부 ID ErpPartCode__c upsert)으로 대신함 / 2026-10-16: 단가 원천은 ERP. 이번 범위는 초기 이관값을 Salesforce 제품 ErpUnitPrice__c(+ 가격표 항목)에 둠(ERP Mock에는 단가 없음). 부품 마스터 동기화는 다음 단계</t>
@@ -1481,6 +1433,81 @@
 재시도: ErpRetryBatch ← ErpRetrySchedulable(매시 정각, "HG ERP 재전송"), Failed와 10분 넘은 Pending 대상
 중복 방지: refId(사용 부품 Id) 기준 ERP 멱등 처리
 삭제: 실패·NeedsReview만 삭제 허용, 대기·완료는 before delete 거부 / 2026-10-16: 삭제된 사용 부품의 재고 되돌림은 Salesforce 표준이 처리(Apex 되돌림 제거, 이중 증가 R6 해소)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>[ SFDC 개발자 온보딩 개인 프로젝트 ]</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-16</t>
+  </si>
+  <si>
+    <t>2026-10-15</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF-01 비고: 단가 원천은 ERP, 이번 범위는 초기 이관값을 Salesforce 제품 ERP 단가(+ 가격표 항목)에 둠, ERP Mock에는 단가 없음, 부품 마스터 동기화는 다음 단계 / IF-03: 사용 부품 삭제 시 재고 되돌림은 Salesforce 표준(Apex 되돌림 제거, R6). 나머지 IF는 변경 없음 / 양식 예시 문구 정리: 표지 프로젝트 문구, 상세 시트 인터페이스 ID·명·설명 칸</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF-02-P</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF_ERP_VANSTOCK_0001 재고 변동 푸시</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERP에서만 생긴 입고·조정을 ERP가 저장 직후 Salesforce Apex REST로 보내 재고(ProductItem)에 변동량만큼 반영</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF-02-R</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF_ERP_VANSTOCK_0001 재고 변동 가져오기</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>Salesforce가 매시 30분 ERP 이력에서 "마지막으로 가져온 번호 이후"만 조회해 푸시로 못 받은 변동을 반영</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF-03</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF_ERP_CONSUME_0001 사용 부품 차감</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>기사가 출동에서 사용 부품을 저장하면 ERP의 같은 위치(창고·기사 차량) 재고를 차감</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF-06</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF_ERP_TRANSFER_0001 재고 이동</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>창고에서 기사 차량으로 보충한 재고 이동(ProductTransfer)을 기사가 수령하면 ERP에서도 출발 위치 차감·도착 위치 증가</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF-07</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF_JUSO_ADDRESS_0001 도로명주소 검색</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>상담원·센터장이 사업장·고객사 주소를 도로명주소 API로 검색해 입력, 사업장은 행정구역 코드로 서비스센터 자동 지정</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
@@ -1699,7 +1726,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1722,11 +1749,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1775,19 +1839,19 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1799,8 +1863,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1808,29 +1884,26 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2503,7 +2576,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:H20"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="8" width="16" customWidth="1"/>
@@ -2512,51 +2585,51 @@
   <sheetData>
     <row r="2" spans="2:8" ht="24" customHeight="1">
       <c r="B2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="24" customHeight="1"/>
-    <row r="7" spans="2:8" ht="26.25">
-      <c r="B7" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+    <row r="7" spans="2:8" ht="25.5">
+      <c r="B7" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+    </row>
+    <row r="11" spans="2:8" ht="20.5">
+      <c r="B11" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-    </row>
-    <row r="11" spans="2:8" ht="19.5">
-      <c r="B11" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
     </row>
     <row r="12" spans="2:8" ht="4.1500000000000004" customHeight="1">
       <c r="B12" s="1"/>
@@ -2568,94 +2641,101 @@
       <c r="H12" s="1"/>
     </row>
     <row r="14" spans="2:8" ht="24" customHeight="1">
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20" t="s">
+        <v>449</v>
+      </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+    </row>
+    <row r="15" spans="2:8" ht="24" customHeight="1">
+      <c r="B15" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="23" t="s">
-        <v>464</v>
-      </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-    </row>
-    <row r="15" spans="2:8" ht="24" customHeight="1">
-      <c r="B15" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23" t="s">
-        <v>466</v>
-      </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
     </row>
     <row r="16" spans="2:8" ht="24" customHeight="1">
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" spans="2:8" ht="24" customHeight="1">
+      <c r="B17" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="23" t="s">
-        <v>467</v>
-      </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-    </row>
-    <row r="17" spans="2:8" ht="24" customHeight="1">
-      <c r="B17" s="21" t="s">
+      <c r="C17" s="19"/>
+      <c r="D17" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+    </row>
+    <row r="18" spans="2:8" ht="24" customHeight="1">
+      <c r="B18" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-    </row>
-    <row r="18" spans="2:8" ht="24" customHeight="1">
-      <c r="B18" s="21" t="s">
+      <c r="C18" s="19"/>
+      <c r="D18" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+    </row>
+    <row r="19" spans="2:8" ht="24" customHeight="1">
+      <c r="B19" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-    </row>
-    <row r="19" spans="2:8" ht="24" customHeight="1">
-      <c r="B19" s="21" t="s">
+      <c r="C19" s="19"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+    </row>
+    <row r="20" spans="2:8" ht="24" customHeight="1">
+      <c r="B20" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-    </row>
-    <row r="20" spans="2:8" ht="24" customHeight="1">
-      <c r="B20" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="B9:H10"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="D19:H19"/>
@@ -2666,13 +2746,6 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="D16:H16"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="B9:H10"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -2688,7 +2761,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2697,51 +2770,51 @@
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.25">
+    <row r="1" spans="1:6" ht="21">
       <c r="A1" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+        <v>10</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
     </row>
     <row r="3" spans="1:6" ht="22.15" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>99</v>
+        <v>4</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>457</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F4" s="3"/>
     </row>
@@ -2750,16 +2823,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="C5" s="38">
-        <v>46311</v>
+        <v>450</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>456</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="F5" s="3"/>
     </row>
@@ -2860,418 +2933,418 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M64"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="34.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.08203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.58203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.08203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="25.9" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
+        <v>16</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
     </row>
     <row r="2" spans="1:13" ht="28.15" customHeight="1">
       <c r="A2" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
+        <v>96</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
     </row>
     <row r="4" spans="1:13" ht="30" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="24" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>107</v>
-      </c>
       <c r="M5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="24" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="M6" t="s">
         <v>108</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="M6" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="24" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="M7" t="s">
         <v>114</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="M7" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="24" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="K8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="M8" t="s">
         <v>121</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="M8" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="24" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="M10" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="24" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="M11" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="M12" t="s">
         <v>140</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="M12" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="24" customHeight="1">
@@ -3360,122 +3433,122 @@
     </row>
     <row r="21" spans="1:12">
       <c r="B21" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="B23" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="B25" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="B27" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="B29" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="B31" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3496,7 +3569,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:V40"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
@@ -3523,770 +3596,760 @@
   <sheetData>
     <row r="2" spans="2:22">
       <c r="B2" s="35"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+    </row>
+    <row r="3" spans="2:22" ht="29">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-    </row>
-    <row r="3" spans="2:22" ht="24">
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="28" t="s">
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="28" t="s">
+      <c r="V5" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" ht="6" customHeight="1"/>
+    <row r="7" spans="2:22">
+      <c r="B7" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="33" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="37" t="s">
+        <v>459</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="31" t="s">
+        <v>460</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="39" t="s">
+        <v>461</v>
+      </c>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="31" t="s">
+      <c r="V7" s="32" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22">
+      <c r="B8" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="33" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8" s="19"/>
+      <c r="S8" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="V5" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" ht="6" customHeight="1">
-      <c r="D6" t="s">
-        <v>108</v>
-      </c>
-      <c r="I6" t="s">
-        <v>166</v>
-      </c>
-      <c r="N6" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="V7" s="32" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" s="22"/>
-      <c r="S8" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
     </row>
     <row r="9" spans="2:22" ht="6" customHeight="1"/>
     <row r="10" spans="2:22">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="B11" s="19"/>
+      <c r="C11" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="19"/>
+      <c r="O11" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="19"/>
+      <c r="C12" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="29" t="s">
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="19"/>
+      <c r="O12" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+    </row>
+    <row r="13" spans="2:22" ht="25.9" customHeight="1">
+      <c r="B13" s="19"/>
+      <c r="C13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="36" t="s">
+      <c r="D13" s="14" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="22"/>
-      <c r="C11" s="28" t="s">
+      <c r="E13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="28" t="s">
+      <c r="F13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="22"/>
-      <c r="O11" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="22"/>
-      <c r="C12" s="31" t="s">
+      <c r="P13" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" s="22"/>
-      <c r="O12" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-    </row>
-    <row r="13" spans="2:22" ht="25.9" customHeight="1">
-      <c r="B13" s="22"/>
-      <c r="C13" s="14" t="s">
+      <c r="Q13" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="R13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="S13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="T13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="U13" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="P13" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="S13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="T13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="U13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="V13" s="22"/>
+      <c r="V13" s="19"/>
     </row>
     <row r="14" spans="2:22" ht="18" customHeight="1">
       <c r="B14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="E14" s="15" t="s">
+      <c r="H14" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="K14" s="16" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="P14" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q14" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="R14" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S14" s="15" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="T14" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U14" s="16" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="V14" s="16" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="2:22" ht="18" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="16"/>
       <c r="E15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="15"/>
       <c r="N15" s="16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Q15" s="15"/>
       <c r="R15" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S15" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="T15" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U15" s="16" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="V15" s="16" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="2:22" ht="18" customHeight="1">
       <c r="B16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="16"/>
       <c r="E16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="15"/>
       <c r="N16" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="Q16" s="15"/>
       <c r="R16" s="15"/>
       <c r="S16" s="15"/>
       <c r="T16" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U16" s="16" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="V16" s="16" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="16"/>
       <c r="E17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L17" s="16"/>
       <c r="M17" s="15"/>
       <c r="N17" s="16" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="O17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P17" s="16" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="Q17" s="15"/>
       <c r="R17" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S17" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T17" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U17" s="16" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="V17" s="16" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="16"/>
       <c r="E18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="15"/>
       <c r="N18" s="16" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="O18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="Q18" s="15"/>
       <c r="R18" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S18" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T18" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U18" s="16" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="V18" s="16" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="16"/>
       <c r="E19" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I19" s="15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="L19" s="16"/>
       <c r="M19" s="15"/>
       <c r="N19" s="16" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="O19" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P19" s="16" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="Q19" s="15"/>
       <c r="R19" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S19" s="15"/>
       <c r="T19" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U19" s="16" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="V19" s="16" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="16"/>
       <c r="E20" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
       <c r="K20" s="16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="15"/>
       <c r="N20" s="16" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="O20" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="P20" s="16" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="Q20" s="15"/>
       <c r="R20" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="S20" s="15"/>
       <c r="T20" s="15"/>
       <c r="U20" s="16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="V20" s="16" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="16"/>
       <c r="E21" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="16" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="15"/>
       <c r="N21" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O21" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Q21" s="15"/>
       <c r="R21" s="15"/>
@@ -4294,295 +4357,295 @@
       <c r="T21" s="15"/>
       <c r="U21" s="16"/>
       <c r="V21" s="16" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="2:22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="16"/>
       <c r="E22" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
       <c r="K22" s="16" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="15"/>
       <c r="N22" s="16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O22" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P22" s="16" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="Q22" s="15"/>
       <c r="R22" s="15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="S22" s="15"/>
       <c r="T22" s="15"/>
       <c r="U22" s="16" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="V22" s="16"/>
     </row>
     <row r="23" spans="2:22" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I23" s="15"/>
       <c r="J23" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M23" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N23" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O23" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P23" s="16" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="Q23" s="15"/>
       <c r="R23" s="15"/>
       <c r="S23" s="15"/>
       <c r="T23" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U23" s="16"/>
       <c r="V23" s="16" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="2:22" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="16" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I24" s="15"/>
       <c r="J24" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O24" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P24" s="16" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q24" s="15"/>
       <c r="R24" s="15"/>
       <c r="S24" s="15"/>
       <c r="T24" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U24" s="16"/>
       <c r="V24" s="16"/>
     </row>
     <row r="25" spans="2:22" ht="18" customHeight="1">
       <c r="B25" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="16"/>
       <c r="E25" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I25" s="15"/>
       <c r="J25" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="15"/>
       <c r="N25" s="16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O25" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P25" s="16" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="Q25" s="15"/>
       <c r="R25" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="S25" s="15"/>
       <c r="T25" s="15"/>
       <c r="U25" s="16" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="V25" s="16" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="2:22" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C26" s="15"/>
       <c r="D26" s="16"/>
       <c r="E26" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="J26" s="15"/>
       <c r="K26" s="16" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="L26" s="16"/>
       <c r="M26" s="15"/>
       <c r="N26" s="16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O26" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P26" s="16" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="Q26" s="15"/>
       <c r="R26" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S26" s="15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="T26" s="15"/>
       <c r="U26" s="16" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" spans="2:22" ht="18" customHeight="1">
       <c r="B27" s="15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="16"/>
       <c r="E27" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="16" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="L27" s="16"/>
       <c r="M27" s="15"/>
       <c r="N27" s="16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O27" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P27" s="16" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="Q27" s="15"/>
       <c r="R27" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S27" s="15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="T27" s="15"/>
       <c r="U27" s="16" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="V27" s="16" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="2:22" ht="18" customHeight="1">
@@ -4610,10 +4673,10 @@
     </row>
     <row r="29" spans="2:22" ht="18" customHeight="1">
       <c r="B29" s="15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="15"/>
@@ -4890,19 +4953,9 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G2:V2"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:T4"/>
-    <mergeCell ref="K5:T5"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="B2:F5"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="V10:V13"/>
@@ -4919,13 +4972,23 @@
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="O11:U11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="I12:L12"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="U7:U8"/>
     <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G2:V2"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:T4"/>
+    <mergeCell ref="K5:T5"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -4941,7 +5004,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:V40"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
@@ -4968,464 +5031,454 @@
   <sheetData>
     <row r="2" spans="2:22">
       <c r="B2" s="35"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+    </row>
+    <row r="3" spans="2:22" ht="29">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-    </row>
-    <row r="3" spans="2:22" ht="24">
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="28" t="s">
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="31" t="s">
+        <v>249</v>
+      </c>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="28" t="s">
+      <c r="V5" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" ht="6" customHeight="1"/>
+    <row r="7" spans="2:22">
+      <c r="B7" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="33" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="37" t="s">
+        <v>462</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="31" t="s">
+        <v>463</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="39" t="s">
+        <v>464</v>
+      </c>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="31" t="s">
+      <c r="V7" s="32" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22">
+      <c r="B8" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="12" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="V5" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" ht="6" customHeight="1">
-      <c r="D6" t="s">
-        <v>114</v>
-      </c>
-      <c r="I6" t="s">
-        <v>257</v>
-      </c>
-      <c r="N6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" s="28" t="s">
+      <c r="H8" s="19"/>
+      <c r="I8" s="32" t="s">
+        <v>252</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="31" t="s">
+      <c r="L8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="V7" s="32" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" s="31" t="s">
+      <c r="N8" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" s="22"/>
+      <c r="R8" s="19"/>
       <c r="S8" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
+        <v>253</v>
+      </c>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
     </row>
     <row r="9" spans="2:22" ht="6" customHeight="1"/>
     <row r="10" spans="2:22">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="B11" s="19"/>
+      <c r="C11" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="19"/>
+      <c r="O11" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="19"/>
+      <c r="C12" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="29" t="s">
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="19"/>
+      <c r="O12" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+    </row>
+    <row r="13" spans="2:22" ht="25.9" customHeight="1">
+      <c r="B13" s="19"/>
+      <c r="C13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="36" t="s">
+      <c r="D13" s="14" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="22"/>
-      <c r="C11" s="28" t="s">
+      <c r="E13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="28" t="s">
+      <c r="F13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="22"/>
-      <c r="O11" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="22"/>
-      <c r="C12" s="31" t="s">
+      <c r="P13" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" s="22"/>
-      <c r="O12" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-    </row>
-    <row r="13" spans="2:22" ht="25.9" customHeight="1">
-      <c r="B13" s="22"/>
-      <c r="C13" s="14" t="s">
+      <c r="Q13" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="R13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="S13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="T13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="U13" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="P13" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="S13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="T13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="U13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="V13" s="22"/>
+      <c r="V13" s="19"/>
     </row>
     <row r="14" spans="2:22" ht="18" customHeight="1">
       <c r="B14" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="O14" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="Q14" s="15"/>
       <c r="R14" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S14" s="15"/>
       <c r="T14" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U14" s="16" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="V14" s="16" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="2:22" ht="18" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="16"/>
       <c r="E15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="15"/>
       <c r="N15" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="Q15" s="15"/>
       <c r="R15" s="15"/>
@@ -5436,147 +5489,147 @@
     </row>
     <row r="16" spans="2:22" ht="18" customHeight="1">
       <c r="B16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E16" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F16" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="H16" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O16" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q16" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="P16" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="R16" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S16" s="15" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="T16" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U16" s="16" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="V16" s="16" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="16"/>
       <c r="E17" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I17" s="15"/>
       <c r="J17" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="L17" s="16"/>
       <c r="M17" s="15"/>
       <c r="N17" s="16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O17" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P17" s="16" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Q17" s="15"/>
       <c r="R17" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S17" s="15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="T17" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U17" s="16"/>
       <c r="V17" s="16" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="16"/>
       <c r="E18" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="15"/>
       <c r="N18" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O18" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="Q18" s="15"/>
       <c r="R18" s="15"/>
@@ -5584,234 +5637,234 @@
       <c r="T18" s="15"/>
       <c r="U18" s="16"/>
       <c r="V18" s="16" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="16"/>
       <c r="E19" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L19" s="16"/>
       <c r="M19" s="15"/>
       <c r="N19" s="16" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="O19" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P19" s="16" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="Q19" s="15"/>
       <c r="R19" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S19" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U19" s="16"/>
       <c r="V19" s="16" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="16"/>
       <c r="E20" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="15"/>
       <c r="N20" s="16" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="O20" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P20" s="16" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="Q20" s="15"/>
       <c r="R20" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S20" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="T20" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U20" s="16"/>
       <c r="V20" s="16" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="16"/>
       <c r="E21" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I21" s="15"/>
       <c r="J21" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="15"/>
       <c r="N21" s="16" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="O21" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="Q21" s="15"/>
       <c r="R21" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S21" s="15"/>
       <c r="T21" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U21" s="16" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="V21" s="16" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="2:22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="16"/>
       <c r="E22" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
       <c r="K22" s="16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="15"/>
       <c r="N22" s="16" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="O22" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="P22" s="16" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="Q22" s="15"/>
       <c r="R22" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="S22" s="15"/>
       <c r="T22" s="15"/>
       <c r="U22" s="16"/>
       <c r="V22" s="16" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23" spans="2:22" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="16"/>
       <c r="E23" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I23" s="15"/>
       <c r="J23" s="15"/>
       <c r="K23" s="16" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="15"/>
       <c r="N23" s="16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="O23" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P23" s="16" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="Q23" s="15"/>
       <c r="R23" s="15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="S23" s="15"/>
       <c r="T23" s="15"/>
@@ -5820,86 +5873,86 @@
     </row>
     <row r="24" spans="2:22" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="16" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I24" s="15"/>
       <c r="J24" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="L24" s="16"/>
       <c r="M24" s="15"/>
       <c r="N24" s="16" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="O24" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P24" s="16" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="Q24" s="15"/>
       <c r="R24" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S24" s="15"/>
       <c r="T24" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U24" s="16"/>
       <c r="V24" s="16" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="2:22" ht="18" customHeight="1">
       <c r="B25" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="16"/>
       <c r="E25" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="I25" s="15"/>
       <c r="J25" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="15"/>
       <c r="N25" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O25" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P25" s="16" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="Q25" s="15"/>
       <c r="R25" s="15"/>
@@ -5907,40 +5960,40 @@
       <c r="T25" s="15"/>
       <c r="U25" s="16"/>
       <c r="V25" s="16" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="2:22" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C26" s="15"/>
       <c r="D26" s="16"/>
       <c r="E26" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I26" s="15"/>
       <c r="J26" s="15"/>
       <c r="K26" s="16" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="L26" s="16"/>
       <c r="M26" s="15"/>
       <c r="N26" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O26" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P26" s="16" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="Q26" s="15"/>
       <c r="R26" s="15"/>
@@ -5948,7 +6001,7 @@
       <c r="T26" s="15"/>
       <c r="U26" s="16"/>
       <c r="V26" s="16" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="2:22" ht="18" customHeight="1">
@@ -5976,10 +6029,10 @@
     </row>
     <row r="28" spans="2:22" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D28" s="16"/>
       <c r="E28" s="15"/>
@@ -6279,19 +6332,9 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G2:V2"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:T4"/>
-    <mergeCell ref="K5:T5"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="B2:F5"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="V10:V13"/>
@@ -6308,13 +6351,23 @@
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="O11:U11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="I12:L12"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="U7:U8"/>
     <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G2:V2"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:T4"/>
+    <mergeCell ref="K5:T5"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -6330,7 +6383,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:V40"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
@@ -6357,805 +6410,795 @@
   <sheetData>
     <row r="2" spans="2:22">
       <c r="B2" s="35"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+    </row>
+    <row r="3" spans="2:22" ht="29">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-    </row>
-    <row r="3" spans="2:22" ht="24">
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="28" t="s">
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="31" t="s">
+        <v>290</v>
+      </c>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="28" t="s">
+      <c r="V5" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" ht="6" customHeight="1"/>
+    <row r="7" spans="2:22">
+      <c r="B7" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="33" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="37" t="s">
+        <v>465</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="39" t="s">
+        <v>467</v>
+      </c>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="31" t="s">
+      <c r="V7" s="32" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" ht="23">
+      <c r="B8" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="12" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="V5" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" ht="6" customHeight="1">
-      <c r="D6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I6" t="s">
-        <v>300</v>
-      </c>
-      <c r="N6" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" s="28" t="s">
+      <c r="H8" s="19"/>
+      <c r="I8" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="31" t="s">
+      <c r="L8" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="M8" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="V7" s="32" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22" ht="22.5">
-      <c r="B8" s="31" t="s">
+      <c r="N8" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="32" t="s">
-        <v>303</v>
-      </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>306</v>
-      </c>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" s="22"/>
+      <c r="R8" s="19"/>
       <c r="S8" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
+        <v>296</v>
+      </c>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
     </row>
     <row r="9" spans="2:22" ht="6" customHeight="1"/>
     <row r="10" spans="2:22">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="B11" s="19"/>
+      <c r="C11" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="19"/>
+      <c r="O11" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="19"/>
+      <c r="C12" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="29" t="s">
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="19"/>
+      <c r="O12" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+    </row>
+    <row r="13" spans="2:22" ht="25.9" customHeight="1">
+      <c r="B13" s="19"/>
+      <c r="C13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="36" t="s">
+      <c r="D13" s="14" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="22"/>
-      <c r="C11" s="28" t="s">
+      <c r="E13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="28" t="s">
+      <c r="F13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="22"/>
-      <c r="O11" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="22"/>
-      <c r="C12" s="31" t="s">
+      <c r="P13" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="30" t="s">
-        <v>309</v>
-      </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" s="22"/>
-      <c r="O12" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-    </row>
-    <row r="13" spans="2:22" ht="25.9" customHeight="1">
-      <c r="B13" s="22"/>
-      <c r="C13" s="14" t="s">
+      <c r="Q13" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="R13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="S13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="T13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="U13" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="P13" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="S13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="T13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="U13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="V13" s="22"/>
+      <c r="V13" s="19"/>
     </row>
     <row r="14" spans="2:22" ht="18" customHeight="1">
       <c r="B14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="E14" s="15" t="s">
+      <c r="H14" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="K14" s="16" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="O14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="P14" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q14" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="R14" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S14" s="15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="T14" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U14" s="16" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="V14" s="16" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="2:22" ht="18" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="16"/>
       <c r="E15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="15"/>
       <c r="N15" s="16"/>
       <c r="O15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="Q15" s="15"/>
       <c r="R15" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S15" s="15"/>
       <c r="T15" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U15" s="16" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="V15" s="16" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
     </row>
     <row r="16" spans="2:22" ht="18" customHeight="1">
       <c r="B16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="16"/>
       <c r="E16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="16"/>
       <c r="O16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="Q16" s="15"/>
       <c r="R16" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S16" s="15"/>
       <c r="T16" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U16" s="16" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="V16" s="16" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="16"/>
       <c r="E17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I17" s="15"/>
       <c r="J17" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="L17" s="16"/>
       <c r="M17" s="15"/>
       <c r="N17" s="16"/>
       <c r="O17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P17" s="16" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="Q17" s="15"/>
       <c r="R17" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S17" s="15"/>
       <c r="T17" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U17" s="16" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="V17" s="16" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="16"/>
       <c r="E18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
       <c r="K18" s="16" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="15"/>
       <c r="N18" s="16"/>
       <c r="O18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="Q18" s="15"/>
       <c r="R18" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S18" s="15"/>
       <c r="T18" s="15"/>
       <c r="U18" s="16" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="V18" s="16"/>
     </row>
     <row r="19" spans="2:22" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="L19" s="16"/>
       <c r="M19" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="O19" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P19" s="16" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="Q19" s="15"/>
       <c r="R19" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S19" s="15"/>
       <c r="T19" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U19" s="16" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="V19" s="16" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="16"/>
       <c r="E20" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="16" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="16"/>
       <c r="O20" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P20" s="16" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Q20" s="15"/>
       <c r="R20" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S20" s="15"/>
       <c r="T20" s="15"/>
       <c r="U20" s="16" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="V20" s="16" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="16"/>
       <c r="E21" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="16" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="M21" s="15"/>
       <c r="N21" s="16"/>
       <c r="O21" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="Q21" s="15"/>
       <c r="R21" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S21" s="15"/>
       <c r="T21" s="15"/>
       <c r="U21" s="16" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="V21" s="16" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="2:22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="16"/>
       <c r="E22" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
       <c r="K22" s="16" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="15"/>
       <c r="N22" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O22" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P22" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Q22" s="15"/>
       <c r="R22" s="15"/>
@@ -7166,37 +7209,37 @@
     </row>
     <row r="23" spans="2:22" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="16"/>
       <c r="E23" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="16" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="15"/>
       <c r="N23" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O23" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P23" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Q23" s="15"/>
       <c r="R23" s="15"/>
@@ -7204,20 +7247,20 @@
       <c r="T23" s="15"/>
       <c r="U23" s="16"/>
       <c r="V23" s="16" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
     </row>
     <row r="24" spans="2:22" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="16"/>
       <c r="E24" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
@@ -7228,19 +7271,19 @@
       <c r="M24" s="15"/>
       <c r="N24" s="16"/>
       <c r="O24" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P24" s="16" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="Q24" s="15"/>
       <c r="R24" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S24" s="15"/>
       <c r="T24" s="15"/>
       <c r="U24" s="16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="V24" s="16"/>
     </row>
@@ -7269,10 +7312,10 @@
     </row>
     <row r="26" spans="2:22" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="D26" s="16"/>
       <c r="E26" s="15"/>
@@ -7618,19 +7661,9 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G2:V2"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:T4"/>
-    <mergeCell ref="K5:T5"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="B2:F5"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="V10:V13"/>
@@ -7647,13 +7680,23 @@
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="O11:U11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="I12:L12"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="U7:U8"/>
     <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G2:V2"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:T4"/>
+    <mergeCell ref="K5:T5"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -7669,7 +7712,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:V40"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
@@ -7696,809 +7739,799 @@
   <sheetData>
     <row r="2" spans="2:22">
       <c r="B2" s="35"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+    </row>
+    <row r="3" spans="2:22" ht="29">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-    </row>
-    <row r="3" spans="2:22" ht="24">
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="28" t="s">
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="28" t="s">
+      <c r="V5" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" ht="6" customHeight="1"/>
+    <row r="7" spans="2:22">
+      <c r="B7" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="33" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="37" t="s">
+        <v>468</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="31" t="s">
+        <v>469</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="39" t="s">
+        <v>470</v>
+      </c>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="31" t="s">
+      <c r="V7" s="32" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" ht="23">
+      <c r="B8" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="33" t="s">
-        <v>355</v>
-      </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="12" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="V5" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" ht="6" customHeight="1">
-      <c r="D6" t="s">
-        <v>135</v>
-      </c>
-      <c r="I6" t="s">
-        <v>356</v>
-      </c>
-      <c r="N6" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" s="28" t="s">
+      <c r="H8" s="19"/>
+      <c r="I8" s="32" t="s">
+        <v>346</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="31" t="s">
+      <c r="L8" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="M8" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="V7" s="32" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22" ht="22.5">
-      <c r="B8" s="31" t="s">
+      <c r="N8" s="32" t="s">
+        <v>347</v>
+      </c>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="32" t="s">
-        <v>303</v>
-      </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="32" t="s">
-        <v>359</v>
-      </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>305</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" s="22"/>
+      <c r="R8" s="19"/>
       <c r="S8" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
+        <v>165</v>
+      </c>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
     </row>
     <row r="9" spans="2:22" ht="6" customHeight="1"/>
     <row r="10" spans="2:22">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="B11" s="19"/>
+      <c r="C11" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="19"/>
+      <c r="O11" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="19"/>
+      <c r="C12" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="29" t="s">
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="19"/>
+      <c r="O12" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+    </row>
+    <row r="13" spans="2:22" ht="25.9" customHeight="1">
+      <c r="B13" s="19"/>
+      <c r="C13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="36" t="s">
+      <c r="D13" s="14" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="22"/>
-      <c r="C11" s="28" t="s">
+      <c r="E13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="28" t="s">
+      <c r="F13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="22"/>
-      <c r="O11" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="22"/>
-      <c r="C12" s="31" t="s">
+      <c r="P13" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="30" t="s">
-        <v>361</v>
-      </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" s="22"/>
-      <c r="O12" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="30" t="s">
-        <v>362</v>
-      </c>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-    </row>
-    <row r="13" spans="2:22" ht="25.9" customHeight="1">
-      <c r="B13" s="22"/>
-      <c r="C13" s="14" t="s">
+      <c r="Q13" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="R13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="S13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="T13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="U13" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="P13" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="S13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="T13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="U13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="V13" s="22"/>
+      <c r="V13" s="19"/>
     </row>
     <row r="14" spans="2:22" ht="18" customHeight="1">
       <c r="B14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="E14" s="15" t="s">
+      <c r="H14" s="15" t="s">
+        <v>300</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="K14" s="16" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="O14" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="P14" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="Q14" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="R14" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S14" s="15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="T14" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U14" s="16" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="V14" s="16" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="2:22" ht="18" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="16"/>
       <c r="E15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="15"/>
       <c r="N15" s="16"/>
       <c r="O15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="Q15" s="15"/>
       <c r="R15" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S15" s="15"/>
       <c r="T15" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U15" s="16" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="V15" s="16" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="2:22" ht="18" customHeight="1">
       <c r="B16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="16"/>
       <c r="E16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="15"/>
       <c r="N16" s="16"/>
       <c r="O16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="Q16" s="15"/>
       <c r="R16" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S16" s="15"/>
       <c r="T16" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U16" s="16" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="V16" s="16"/>
     </row>
     <row r="17" spans="2:22" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="16"/>
       <c r="E17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="M17" s="15"/>
       <c r="N17" s="16"/>
       <c r="O17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P17" s="16" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="Q17" s="15"/>
       <c r="R17" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S17" s="15"/>
       <c r="T17" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U17" s="16" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="V17" s="16"/>
     </row>
     <row r="18" spans="2:22" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="16"/>
       <c r="E18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="15"/>
       <c r="N18" s="16"/>
       <c r="O18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="Q18" s="15"/>
       <c r="R18" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S18" s="15"/>
       <c r="T18" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U18" s="16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="V18" s="16" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="16"/>
       <c r="E19" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
       <c r="K19" s="16" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="L19" s="16"/>
       <c r="M19" s="15"/>
       <c r="N19" s="16"/>
       <c r="O19" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P19" s="16" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="Q19" s="15"/>
       <c r="R19" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S19" s="15"/>
       <c r="T19" s="15"/>
       <c r="U19" s="16" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="V19" s="16"/>
     </row>
     <row r="20" spans="2:22" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N20" s="16" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="O20" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P20" s="16" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="Q20" s="15"/>
       <c r="R20" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S20" s="15"/>
       <c r="T20" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U20" s="16" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="V20" s="16" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="16"/>
       <c r="E21" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="16" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="M21" s="15"/>
       <c r="N21" s="16"/>
       <c r="O21" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Q21" s="15"/>
       <c r="R21" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S21" s="15"/>
       <c r="T21" s="15"/>
       <c r="U21" s="16" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="V21" s="16" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" spans="2:22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="16"/>
       <c r="E22" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="16" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="M22" s="15"/>
       <c r="N22" s="16"/>
       <c r="O22" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P22" s="16" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="Q22" s="15"/>
       <c r="R22" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S22" s="15"/>
       <c r="T22" s="15"/>
@@ -8507,41 +8540,41 @@
     </row>
     <row r="23" spans="2:22" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="16"/>
       <c r="E23" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="16" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="16"/>
       <c r="O23" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P23" s="16" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="Q23" s="15"/>
       <c r="R23" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S23" s="15"/>
       <c r="T23" s="15"/>
@@ -8550,35 +8583,35 @@
     </row>
     <row r="24" spans="2:22" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="16"/>
       <c r="E24" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
       <c r="K24" s="16" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="L24" s="16"/>
       <c r="M24" s="15"/>
       <c r="N24" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O24" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P24" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="15"/>
       <c r="R24" s="15"/>
@@ -8586,7 +8619,7 @@
       <c r="T24" s="15"/>
       <c r="U24" s="16"/>
       <c r="V24" s="16" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" spans="2:22" ht="18" customHeight="1">
@@ -8614,10 +8647,10 @@
     </row>
     <row r="26" spans="2:22" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="D26" s="16"/>
       <c r="E26" s="15"/>
@@ -8963,19 +8996,9 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G2:V2"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:T4"/>
-    <mergeCell ref="K5:T5"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="B2:F5"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="V10:V13"/>
@@ -8992,13 +9015,23 @@
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="O11:U11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="I12:L12"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="U7:U8"/>
     <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G2:V2"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:T4"/>
+    <mergeCell ref="K5:T5"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -9014,7 +9047,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:V40"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
@@ -9041,656 +9074,646 @@
   <sheetData>
     <row r="2" spans="2:22">
       <c r="B2" s="35"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="37" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="19"/>
+      <c r="V2" s="19"/>
+    </row>
+    <row r="3" spans="2:22" ht="29">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-    </row>
-    <row r="3" spans="2:22" ht="24">
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="28" t="s">
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="31" t="s">
+        <v>378</v>
+      </c>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="28" t="s">
+      <c r="V5" s="11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" ht="6" customHeight="1"/>
+    <row r="7" spans="2:22">
+      <c r="B7" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="33" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="37" t="s">
+        <v>471</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="31" t="s">
+        <v>472</v>
+      </c>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="39" t="s">
+        <v>473</v>
+      </c>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="31" t="s">
+      <c r="V7" s="32" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22">
+      <c r="B8" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="33" t="s">
-        <v>391</v>
-      </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="12" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="32" t="s">
+        <v>380</v>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="V5" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" ht="6" customHeight="1">
-      <c r="D6" t="s">
-        <v>140</v>
-      </c>
-      <c r="I6" t="s">
-        <v>392</v>
-      </c>
-      <c r="N6" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" s="28" t="s">
+      <c r="H8" s="19"/>
+      <c r="I8" s="32" t="s">
+        <v>381</v>
+      </c>
+      <c r="J8" s="19"/>
+      <c r="K8" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="N7" s="32" t="s">
+      <c r="L8" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="V7" s="32" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" s="31" t="s">
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="32" t="s">
-        <v>395</v>
-      </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="32" t="s">
-        <v>396</v>
-      </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" s="22"/>
+      <c r="R8" s="19"/>
       <c r="S8" s="32" t="s">
-        <v>307</v>
-      </c>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
+        <v>296</v>
+      </c>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="19"/>
     </row>
     <row r="9" spans="2:22" ht="6" customHeight="1"/>
     <row r="10" spans="2:22">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="36" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="B11" s="19"/>
+      <c r="C11" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="N11" s="19"/>
+      <c r="O11" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="19"/>
+      <c r="C12" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="29" t="s">
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="34" t="s">
+        <v>383</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="19"/>
+      <c r="O12" s="34" t="s">
+        <v>385</v>
+      </c>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+    </row>
+    <row r="13" spans="2:22" ht="25.9" customHeight="1">
+      <c r="B13" s="19"/>
+      <c r="C13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="36" t="s">
+      <c r="D13" s="14" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="22"/>
-      <c r="C11" s="28" t="s">
+      <c r="E13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="28" t="s">
+      <c r="F13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="22"/>
-      <c r="O11" s="33" t="s">
-        <v>397</v>
-      </c>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="22"/>
-      <c r="C12" s="31" t="s">
+      <c r="P13" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="30" t="s">
-        <v>398</v>
-      </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="30" t="s">
-        <v>399</v>
-      </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="N12" s="22"/>
-      <c r="O12" s="30" t="s">
-        <v>400</v>
-      </c>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="30" t="s">
-        <v>401</v>
-      </c>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-    </row>
-    <row r="13" spans="2:22" ht="25.9" customHeight="1">
-      <c r="B13" s="22"/>
-      <c r="C13" s="14" t="s">
+      <c r="Q13" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="R13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="S13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="T13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="U13" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="P13" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="S13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="T13" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="U13" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="V13" s="22"/>
+      <c r="V13" s="19"/>
     </row>
     <row r="14" spans="2:22" ht="18" customHeight="1">
       <c r="B14" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I14" s="15"/>
       <c r="J14" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="O14" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P14" s="16" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="Q14" s="15"/>
       <c r="R14" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S14" s="15"/>
       <c r="T14" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U14" s="16" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="V14" s="16" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" spans="2:22" ht="18" customHeight="1">
       <c r="B15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="16"/>
       <c r="E15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="15"/>
       <c r="N15" s="16"/>
       <c r="O15" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="Q15" s="15"/>
       <c r="R15" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S15" s="15" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="T15" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U15" s="16"/>
       <c r="V15" s="16" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16" spans="2:22" ht="18" customHeight="1">
       <c r="B16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C16" s="15"/>
       <c r="D16" s="16"/>
       <c r="E16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="G16" s="15"/>
       <c r="H16" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="15"/>
       <c r="N16" s="16"/>
       <c r="O16" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="Q16" s="15"/>
       <c r="R16" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S16" s="15"/>
       <c r="T16" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U16" s="16"/>
       <c r="V16" s="16" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="18" customHeight="1">
       <c r="B17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="16"/>
       <c r="E17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="G17" s="15"/>
       <c r="H17" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I17" s="15"/>
       <c r="J17" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="L17" s="16"/>
       <c r="M17" s="15"/>
       <c r="N17" s="16"/>
       <c r="O17" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P17" s="16" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="Q17" s="15"/>
       <c r="R17" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S17" s="15"/>
       <c r="T17" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U17" s="16"/>
       <c r="V17" s="16" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="18" customHeight="1">
       <c r="B18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="16"/>
       <c r="E18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="15"/>
       <c r="N18" s="16"/>
       <c r="O18" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="Q18" s="15"/>
       <c r="R18" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="S18" s="15"/>
       <c r="T18" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U18" s="16"/>
       <c r="V18" s="16" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="18" customHeight="1">
       <c r="B19" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="M19" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O19" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P19" s="16" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="Q19" s="15"/>
       <c r="R19" s="15"/>
@@ -9698,42 +9721,42 @@
       <c r="T19" s="15"/>
       <c r="U19" s="16"/>
       <c r="V19" s="16" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="18" customHeight="1">
       <c r="B20" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="16"/>
       <c r="E20" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="15"/>
       <c r="N20" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O20" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P20" s="16" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="Q20" s="15"/>
       <c r="R20" s="15"/>
@@ -9741,236 +9764,236 @@
       <c r="T20" s="15"/>
       <c r="U20" s="16"/>
       <c r="V20" s="16" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="18" customHeight="1">
       <c r="B21" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="16" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I21" s="15"/>
       <c r="J21" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="L21" s="16"/>
       <c r="M21" s="15"/>
       <c r="N21" s="16" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="O21" s="15" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="Q21" s="15"/>
       <c r="R21" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S21" s="15"/>
       <c r="T21" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U21" s="16" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="V21" s="16" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="2:22" ht="18" customHeight="1">
       <c r="B22" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="16"/>
       <c r="E22" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
       <c r="K22" s="16" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="15"/>
       <c r="N22" s="16" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="O22" s="15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P22" s="16" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="Q22" s="15"/>
       <c r="R22" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S22" s="15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="T22" s="15"/>
       <c r="U22" s="16" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="V22" s="16"/>
     </row>
     <row r="23" spans="2:22" ht="18" customHeight="1">
       <c r="B23" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="16"/>
       <c r="E23" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J23" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="15"/>
       <c r="N23" s="16" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="O23" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="P23" s="16" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="Q23" s="15"/>
       <c r="R23" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S23" s="15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="T23" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U23" s="16"/>
       <c r="V23" s="16"/>
     </row>
     <row r="24" spans="2:22" ht="18" customHeight="1">
       <c r="B24" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="16"/>
       <c r="E24" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I24" s="15"/>
       <c r="J24" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="L24" s="16"/>
       <c r="M24" s="15"/>
       <c r="N24" s="16" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="O24" s="15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="P24" s="16" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="Q24" s="15"/>
       <c r="R24" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S24" s="15"/>
       <c r="T24" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U24" s="16"/>
       <c r="V24" s="16" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="2:22" ht="18" customHeight="1">
       <c r="B25" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="16"/>
       <c r="E25" s="15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
       <c r="K25" s="16" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="15"/>
       <c r="N25" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="O25" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="P25" s="16" t="s">
         <v>434</v>
-      </c>
-      <c r="O25" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="P25" s="16" t="s">
-        <v>449</v>
       </c>
       <c r="Q25" s="15"/>
       <c r="R25" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S25" s="15"/>
       <c r="T25" s="15"/>
@@ -9979,88 +10002,88 @@
     </row>
     <row r="26" spans="2:22" ht="18" customHeight="1">
       <c r="B26" s="15" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C26" s="15"/>
       <c r="D26" s="16"/>
       <c r="E26" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="J26" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="L26" s="16"/>
       <c r="M26" s="15"/>
       <c r="N26" s="16" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="O26" s="15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P26" s="16" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="Q26" s="15"/>
       <c r="R26" s="15" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="S26" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="T26" s="15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27" spans="2:22" ht="18" customHeight="1">
       <c r="B27" s="15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="16"/>
       <c r="E27" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="I27" s="15"/>
       <c r="J27" s="15"/>
       <c r="K27" s="16" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="L27" s="16"/>
       <c r="M27" s="15"/>
       <c r="N27" s="16" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="O27" s="15" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="P27" s="16" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="Q27" s="15"/>
       <c r="R27" s="15"/>
@@ -10071,15 +10094,15 @@
     </row>
     <row r="28" spans="2:22" ht="18" customHeight="1">
       <c r="B28" s="15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="16"/>
       <c r="E28" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
@@ -10089,25 +10112,25 @@
       <c r="L28" s="16"/>
       <c r="M28" s="15"/>
       <c r="N28" s="16" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="O28" s="15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P28" s="16" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="Q28" s="15"/>
       <c r="R28" s="15" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="S28" s="15"/>
       <c r="T28" s="15"/>
       <c r="U28" s="16" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="V28" s="16" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
     </row>
     <row r="29" spans="2:22" ht="18" customHeight="1">
@@ -10135,10 +10158,10 @@
     </row>
     <row r="30" spans="2:22" ht="18" customHeight="1">
       <c r="B30" s="15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="D30" s="16"/>
       <c r="E30" s="15"/>
@@ -10392,19 +10415,9 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G2:V2"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:T4"/>
-    <mergeCell ref="K5:T5"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="C10:L10"/>
-    <mergeCell ref="S12:U12"/>
-    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="B2:F5"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="V10:V13"/>
@@ -10421,13 +10434,23 @@
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="O11:U11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="C10:L10"/>
+    <mergeCell ref="S12:U12"/>
+    <mergeCell ref="I12:L12"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="U7:U8"/>
     <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G2:V2"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:T4"/>
+    <mergeCell ref="K5:T5"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
@@ -10438,6 +10461,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b82e25f1-f1d4-4b57-be84-1f5ad188becc" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="355e9163-e205-4f55-8724-e062aa2d762e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x01010065F9ABE2E9073F4DBEFD3A0E4E804736" ma:contentTypeVersion="15" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="e21f2c0381dcdb676ff4d058d9391828">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="355e9163-e205-4f55-8724-e062aa2d762e" xmlns:ns3="b82e25f1-f1d4-4b57-be84-1f5ad188becc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74ede542eddc1547cf48ce9271227341" ns2:_="" ns3:_="">
     <xsd:import namespace="355e9163-e205-4f55-8724-e062aa2d762e"/>
@@ -10672,17 +10706,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b82e25f1-f1d4-4b57-be84-1f5ad188becc" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="355e9163-e205-4f55-8724-e062aa2d762e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -10692,6 +10715,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D26ECB15-3FDD-4C35-92F9-4264B0EBD877}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b82e25f1-f1d4-4b57-be84-1f5ad188becc"/>
+    <ds:schemaRef ds:uri="355e9163-e205-4f55-8724-e062aa2d762e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7EA8EB8-8178-41E0-9206-19F9D83219D3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10710,17 +10744,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D26ECB15-3FDD-4C35-92F9-4264B0EBD877}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b82e25f1-f1d4-4b57-be84-1f5ad188becc"/>
-    <ds:schemaRef ds:uri="355e9163-e205-4f55-8724-e062aa2d762e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0718495D-57A5-42EE-AAC1-AEB28EB8AEEF}">
   <ds:schemaRefs>
